--- a/data/market/KB Daily FX report.xlsx
+++ b/data/market/KB Daily FX report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\market\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A53E66A-C4E6-4EBC-B285-FE805ADB7092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD80D8CC-56B7-4AE3-9926-1A3EB61A9A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65727F71-2509-4956-B65C-BBDF77D7D3C0}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3650" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="233">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -27207,6 +27207,49 @@
   <si>
     <t>[달러/원 환율] 협상 결렬 등 대내외적 원화 약세 압력에 상방 우세 전망 전일 달러/원 환율은 미·이란 종전 협상 진정 기대에 1,475원으로 하락 개장한 이후 저가 매수세 유입되며 하방은 제한된 흐름. 이후로도 종전 합의 불확실성에 국제유가 및 달러화 지수가 반등하며 달러/원 역시 낙폭 꾸준히 축소. 반면 외국인의 국내주식 순매수세는 환율 상방을 제한, 전일 종가 대비 보합인 1,482.5원에 정규장 마감. 야간장에서는 미·이란 종전 협상 결과 대기하며 1,483.2원으로 마감. 역외 NDF 환율은 3.00원 상승한 1,484.20원에 최종 호가 금일 달러/원 환율은 미·이란 종전 협상 불발 영향에 상승 개장 예상. 협상 결렬되고 군사적 긴장 재차 고조되며 안전자산 선호 심리 확산할 듯. 달러화 지수는 이미 99pt 상회하며 글로벌 달러 강세 국면. 국제유가 역시 지난주 하락 분을 상당 폭 되돌리며 배럴당 100달러 돌파 (WTI 선물). 한편 이번 주 예정된 외국인 배당과 역송금 수요는 수급적 부담 요인. 금일 환율은 대내외적 원화 약세 압력에 큰 상방 변동성 보일 전망 [글로벌 동향] 美 물가에 전쟁 여파 반영, 소비심리 악화에 달러화 약세 전일 미 달러화는 미·이란 종전 협상 대기 속 미국 물가 등 지표 결과 소화하며 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.11% 하락한 98.70pt 기록. 미·이란 양국은 협상을 앞두고 다소 강경한 발언을 하며 경계감이 고조. 트럼프 대통령은 합의 결렬 시, 대대적인 공격에 나설 수 있다고 언급. 이란 군 관계자는 여전히 완전한 대비 태세를 유지 중이라고 밝힘. 미국의 3월 소비자물가지수는 유가 급등 영향에 전월대비 0.9% 상승. 하지만 예상에 부합해 시장에 미친 영향은 제한적. 에너지와 식료품 제외 근원 소비자물가는 0.2% 상승에 그치며 예상치 (+0.3%) 하회. 즉 전쟁에 따른 유가 급등 영향을 제외하면 전반적인 물가 압력은 강하지 않았던 것으로 확인. 미시간대 4월 소비자심리지수는 47.6pt로 예상치 (51.5pt) 및 전월치 (53.3pt) 하회. 반면 1년 후 기대 인플레이션율은 4.8%로 전월대비 1.0%p 급등 [마켓 이슈] 대외 불확실성 속 외국인 배당, 다시 커지는 환율 상방 리스크 미국과 이란의 종전 협상이 불발되며 중동 전황은 여전히 불안정한 상황. 지난주 환율 하락은 전쟁 종료보다는 일시 휴전을 반영한 성격이 강함. 따라서 협상 결렬이나 중동 긴장 재확대 시 유가와 환율은 다시 빠르게 반등할 수 있음. 문제는 여기에 4월 배당 시즌이 겹쳐있다는 점임. 금주 외국인 배당 지급액은 32억 달러로 주차별 최대 규모. 즉 이번 주는 대외 불확실성이 여전히 큰 상황에서, 수급 부담까지 가중된 한 주. 물론 지급된 배당금 전부가 즉시 달러 매수로 연결되지는 않을 수 있음. 하지만 시장은 이런 불확실한 상황 속에서 실제 물량보다 잠재적 달러 수요 자체에 민감하게 반응할 것임. 종전 합의가 어그러지면 환율 상방이 자극될 텐데, 여기에 '배당'이라는 재료가 상방 압력을 더욱 가중시킬 수 있음. 즉 중동 불확실성이 재차 고조되는 가운데 배당 관련 수급 부담까지 겹치면, 금주 환율은 다시 1,500원 부근까지 상승할 수 있음</t>
   </si>
+  <si>
+    <t>느낌 좋은 협상, 다시 빠질 환율 [금일 달러/원 환율 1,475~1,485원 전망]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이민혁</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달러/원 환율] 위험선호 심리 회복 및 유가 하락에 1,480원 하회 시도 전일 달러/원 환율은 미·이란 종전 협상 결렬에 따른 국제유가 급등과 위험자산 회피 심리에 1,495원으로 상승 개장. 장초반 1,499원까지 상승 폭 확대했으나, 수출 네고 출회와 역외 고점 매도 추정 물량에 추가 상승은 제한됨. 이후에도 꾸준히 상승 폭 축소되며 1,490원 하회, 전일 종가 대비 6.7원 상승한 1,489.2원에 정규장 마감. 야간장에서는 미·이란 재협상 기대에 1,482.7원으로 하락 마감. 역외 NDF 환율은 9.40원 하락한 1,478.60원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래 감안해 1,480원 부근 개장 예상. 미·이란 물밑 협상으로 종전 기대 되살아나며 위험자산 선호 심리 역시 회복. 이에 따른 국제유가 및 달러화 지수 하락이 달러/원 하락의 주요인이 될 전망. 더불어 금일 국내증시에서는 외국인의 주식 순매수 전환 기대. 이에 따른 원화 강세에 1,480원 하회 시도할 듯. 다만 외국인 배당 지급과 이에 대한 역송금 수요가 하단 지지 요소 [글로벌 동향] 미국의 호르무즈 해협 봉쇄에도 재협상 기대에 달러 약세 전일 미 달러화는 미·이란 물밑 협상에 따른 종전 기대에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.29% 하락한 98.42pt 기록. 전날 미국은 군함으로 호르무즈 해협 통제 시작. 하지만 이내 양국 물밑 협상이 이뤄지고 있단 소식에 분위기 반전. 트럼프는 이란 측으로부터 연락을 받았고, 그들은 합의를 원한다고 밝힘. 다만 그는 이란의 핵 포기 없이는 합의도 없을 것이라고 강조. WTI 국제유가는 협상 결렬 직후 아시아장에서 배럴당 105달러까지 급등. 이후 재협상 기대 반영하며 99달러까지 상승 폭 축소. 이에 미 국채금리도 장단기물 대체로 하락 전환. 뉴욕증시는 위험선호 회복에 3대 지수 모두 상승 마감. 한편 유로화는 헝가리의 유로화 도입 계획 소식에 강세. 헝가리 총선에서 친유럽 성향인 페테르 마자르의 야당이 과반 차지. 마자르 총리는 경제 검토 이후 유로화 도입 일정을 확정할 것이라고 밝힘 [마켓 이슈] 잡음 제외한 균형환율은 1,330원대, 관건은 전쟁 장기화 여부 최근 달러/원 환율은 중동 리스크, 유가 급등, 배당 역송금 같은 요인들이 겹치며 높은 레벨에 머물고 있음. 한편 한미 펀더멘털을 반영한 장기균형환율은 현재 1,330원대로 추정됨. 장기균형환율이란 뉴스나 수급 등 잡음을 제외하고 양국 생산성 및 성장률과 정책금리 등 펀더멘털만을 반영한 균형 레벨. 즉 현재 달러/원은 균형 레벨을 상당 폭 웃도는 전형적인 오버슈팅 국면으로 해석. 따라서 중동 긴장이 완화되고, 배당 등으로 자극됐던 달러 수요가 진정된다면 환율도 비교적 빠르게 균형 수준으로 되돌려질 전망. 다만 전쟁과 고유가가 길어지면 상황이 달라질 수 있음. 이 경우에는 지금의 단기 충격이 더 이상 잡음에 그치지 않고, 실제 펀더멘털 변화로 이어질 수 있기 때문. 특히 한국 경제는 미국보다 에너지 수입 의존도가 높아 고유가에 더욱 취약한 구조. 이렇게 되면 지금은 1,330원대로 추정되는 장기균형환율이 점차 상향 조정될 수 있음</t>
+  </si>
+  <si>
+    <t>미국 ADP 고용 부진에 달러 연속되는 약세 [금일 달러/원 환율 1,460~1,470원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 미국 금리인하 기대와 달러 약세에 1,460원대 등락 전망 전일 달러/원 환율은 개장 이후 역외 달러 약세에도 다시 1,470원대까지 상승했으나, 오후 들어 역외 달러 약세를 반영하며 하락, 그럼에도 종가는 0.4원 하락에 그친 1,468.0원에 마감함. 야간에는 미국 ADP 고용 부진으로 달러가 약세를 보임에 따라 1,466.9원으로 더 하락했으며, NDF 역외에서는 달러 낙폭이 다소 축소되고 뉴욕증시 반등 등으로 0.25원 상승함 금일 달러/원 환율은 전일 미 달러화 지수 하락과 야간장 및 역외에서도 60원대 중반에 머무름에 따라 1,460원대에서 등락할 것으로 예상됨. 최근 달러화는 6거래일 연속 하락하고 있는데, 다음주 FOMC 회의에서 연준의 금리인하 기대를 반영하고 있기 때문. 다만, 달러 약세 폭도 크지 않으며, 원화는 여전히 장중 달러 롱 심리의 지속과 수급적으로 하방이 제한되고 있어 금일에도 1,460원대에서 등락이 예상됨 [글로벌 동향] 미국 고용 부진과 영국 재정 우려 완화에 달러 큰 폭 하락 전일 미 달러화는 고용지표 결과의 예상 하회 소식과 영국 파운드화 강세 등의 영향에 0.43% 하락함. 미국 11월 ADP 민간 고용은 3만 2천명이 감소, 1만명 증가할 것으로 예상된 것에 비해 크게 저조함. 전월치는 4만 2천명 증가에서 4만 7천명 증가로 상향 수정됨. 뒤늦게 발표된 미국 9월 수입물가와 수출물가 모두 전월대비 보합, 광공업 생산은 0.1% 증가에 불과함. 11월 ISM 서비스업 지수는 52.4에서 52.6으로 소폭 상회함. 미국 국채 금리는 장단기에서 소폭 하락했으며, 뉴욕증시는 개장 초반 약세에서 반등에 성공함. 한편 영국에서는 여러 정책 조합을 통해 재정적자가 축소될 것이라는 긍정적 소식이 전해졌고, 영국 파운드/달러는 1.03% 급등함. 이렇듯 미국 경제지표 부진과 영국 재정 우려 완화 등에 달러는 약세를, 지수는 99pt를 하회함 [마켓 이슈] ADP 고용 결과로 더 심각해진 부진, 연준 금리인하 기대 상승 전일 발표된 미국 11월 ADP 민간 고용이 전월보다 3만 2천명 감소, 9월 감소에 이어 10월 증가, 11월 더 큰 감소를 기록함. 노동통계국에서의 발표가 지연됨에 따라 미국 고용을 확인하는 지표라는 점에서 ADP 민간 고용 부진은 미국 고용침체가 매우 심각해졌음을 시사함. 산업별로는 건설, 제조업에서 감소, 서비스업에서는 보건의료, 건강레저 등에서만 고용이 증가함. 연방정부 셧다운이 종료되었어도 노동통계국에서 가계 조사를 하지 못함에 따라 10월 고용 보고서는 발표되지 않을 가능성이 높음. 11월 고용 보고서는 12월 초에서 중순으로 발표가 연기될 예정임. 이번 고용 결과는 다음주 예정된 미국 연준의 FOMC 회의에 참고자료로 활용될 것임. 고용 부진이 예상보다 심각했다면 12월 연준 위원들의 경기판단, 경제전망 모두 하향 수정될 수 있으며, 추가 금리인하 기대는 달러에 약세 요인으로 작용할 것으로 판단됨</t>
+  </si>
+  <si>
+    <t>약 달러, 위험선호에도 원화는 제자리 걸음 [금일 달러/원 환율 1,465~1,473원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 대외 여건 상 하방 우세, 여전히 역내 수급 불균형은 변수 전일 달러/원 환율은 뉴욕증시 하락 등 위험회피 분위기에 1,471원으로 상승 개장한 이후 장초반 73원까지 상승 폭 확대. 이후 외환당국 경계에 상단 인식이 형성되었고, 국내증시 호조 및 외국인 주식 순매수에 하락 전환하며 1,470원선 하회. 이후 꾸준히 유입된 결제수요에 하단 지지되며 전일 종가 대비 1.5원 하락한 1,468.4원에 정규장 마감. 야간장에서는 특별한 움직임 없이 제한된 범위 내에서 등락하며 1,469.4원에 마감. 역외 NDF 환율은 보합 수준인 1,466.10원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세와 역외 거래를 감안해 소폭 하락 개장 예상. 연준 차기 의장 이슈 및 ECB 동결 기대에 달러 약세. 뉴욕증시 회복 등 위험선호는 원화에 긍정적. 즉 대외 여건 상 달러/원의 하방 압력은 커지고 있는 상태. 다만 여전히 역내 수급 불균형 이어지며 하단이 지지되는 형국. 금일 환율도 역내 수출입 관련 물량과 커스터디 플로우에 연동. 외환당국 경계하며 1,470원대 초중반에서 상단 형성될 전망 [글로벌 동향] 연준 차기 의장, ECB 인하 사이클 종료 기대에 달러 약세 전일 미 달러화는 트럼프 대통령의 연준 의장 지명 발언 소화하며 약보합. 주요 6개국 통화로 구성된 달러화 지수는 0.07% 하락한 99.34pt 기록. 트럼프는 차기 연준 의장 후보로 10명을 검토했고, 이제 1명으로 압축되었다고 발언. 그는 아마 내년 초에 의장 지명 발표가 있을 것이라고 밝힘. 더불어 그는 케빈 해싯 백악관 위원장을 거론, 그가 잠재적 의장이라고 덧붙임. 폴리마켓의 케빈 해싯 지명 확률은 80%대 기록. 트럼프의 연준 의장 발언 이후 미 국채금리는 단기물 위주로 하락. FedWatch의 12월 금리인하 확률은 90% 수준에 육박. 뉴욕증시는 연준 의장 지명 이슈 등 위험선호에 3대 지수 모두 상승. 유로화는 유로존 인플레이션 우려에 강세. 유로존 11월 소비자물가지수는 전년비 2.2% 상승 (예상 +2.1%). 이에 ECB 인하 기대 약화, 유로/달러는 1.16달러 상회. 오스트리아 중앙은행 총재는 ECB 인하 사이클 종료가 기본 시나리오라고 언급 [마켓 이슈] 금일 저녁 ADP 민간고용 발표, 연준 금리인하 명분 강화 재료 금일 저녁 발표될 미국의 11월 ADP 민간고용이 시장의 핵심 이벤트로 부상. 정부의 공식 고용통계 확인이 제한된 상황 속, ADP 통계 중요성이 부각될 수밖에 없는 상황. 컨센서스는 전월대비 1만명 증가로, 10월 수치 (+4.2만명)보다 큰 폭 둔화 예상. 이는 민간 부문의 신규 고용 창출 기대가 크게 약화되고 있음을 시사. 또한 연준 내부적으로 언급된 적정 고용 (breakeven)이 5~10만명이라는 점을 감안. 즉, ADP만 놓고 보면, 미국 신규 고용은 적정 수준을 크게 하회. 최근 추세는 ADP와 NFP 모두 완만한 하향 흐름을 보이는 상황. 이는 연준이 다음주 FOMC에서 통화정책 완화 명분을 강화할 수 있는 핵심 논거. 올해 연준 인하 (9월, 10월)의 근거가 물가보다는 주로 고용 리스크에 방점이 찍혀있었기 때문. 이 같은 요인들은 달러의 약세 압력을 가중시켜 달러/원에는 하방 요인으로 작용할 가능성. 즉, 금일 ADP 발표 직후 달러 방향 변화를 주시할 필요</t>
+  </si>
+  <si>
+    <t>꽁꽁 얼어붙은 투심 위로 원화가 횡보합니다 [금일 달러/원 환율 1,465~1,475원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 대외적 상하방 요인 혼재, 수급적으로도 막혀있는 상하단 전일 달러/원 환율은 연준 금리인하 기대에 따른 달러화 약세, 일본 금리인상 기대로 인한 엔화 강세 등에 하락 개장. 이후 결제수요가 꾸준히 유입되며 환율 하단이 지속 상향, 외국인 국내주식 순매도까지 겹치며 1,470원 부근까지 반등. 이후 당국 경계에 혼조세, 전일 종가 대비 0.7원 하락한 1,469.9원에 정규장 마감. 야간장에서는 미국 제조업 경기 위축에도 엔 캐리 청산 우려 등 위험회피에 낙폭 제한되며 1,468.0원에 마감. 역외 NDF 환율은 1.95원 상승한 1,469.40원에 최종 호가 금일 달러/원 환율은 간밤 달러 약세에도 역외 거래 감안해 1,470원 부근 상승 개장 예상. 미 제조업 경기 위축 및 BOJ 인상 기대는 달러에 약세 요인. 하지만 지정학 갈등 및 엔 캐리 청산 우려 등 위험회피심리가 원화 강세에 제동. 즉 대외적 요인은 달러/원 방향에 중립적. 역내 수급적으로는 여전히 달러 매수 우위 장세 지속. 네고물량 부족, 결제수요는 꾸준히 유입되며 하단 지지. 다만 당국 경계가 상단 제약하는 요소로 작용 [글로벌 동향] 미 제조업 경기 위축, BOJ 인상 기대에 엔 캐리 청산 우려 전일 미 달러화는 미국 제조업 경기 위축 조짐에 따른 약세 압력에도 위험회피심리에 약보합. 주요 6개국 통화로 구성된 달러화 지수는 0.05% 하락한 99.41pt 기록. 미국 공급관리협회 (ISM)의 11월 제조업 지수는 48.2pt로 기준치 50pt 하회. 또한 예상치 (49.0pt) 및 전월치 (48.7pt)를 하회하며 모멘텀 둔화. 하위 지수로는 고용 (44.0pt) 및 신규주문 (47.4pt)이 부진. 반면, 생산 (51.4pt) 및 가격 (58.5pt) 지수는 양호해 지수별 혼조 흐름. 우크라이나의 러시아 공격과 미국의 베네수엘라 압박 등 지정학 이벤트는 위험회피심리 자극. 더불어 일본 BOJ 금리인상 기대로 엔 캐리 청산 가능성 부각되며 글로벌 투심 위축. 일본 2년물 국채금리는 2008년 이후 처음 1% 상회, 10년물 역시 급등하며 2008년 이후 최고치. 뉴욕증시는 지정학 이벤트 및 엔 캐리 청산 우려 등 위험회피심리에 3대 지수 모두 하락 마감 [마켓 이슈] 꼬인 수급의 속사정, 국내로 환류되지 않은 해외자회사 유보금 최근 환율 상승의 주요 배경인 '수급 불균형'에서 국내 기업의 막대한 해외유보금에 주목. 국내 기업의 해외자회사 유보금은 2025년 9월 1,144억 달러로 역대 최대치 (누적 기준). 특히 올해 들어 유보금 증가액은 66.5억 달러로, 전년동기대비 59.7% 급증. 이는 해외에서 발생한 직접투자 배당 수익이 국내로 충분히 환류되지 않았음을 시사. 22년 말 도입된 '해외자회사 배당금 익금불산입 제도'가 일시적으로 수익 송금 확대 유도. 하지만 최근 흐름은 유보액 축적 속도가 다시 송금 흐름을 상회하는 모습. 최근 고환율 국면에서 기업의 '달러 보유 선호'가 강화된 데다, 해외투자·현지재투자 확대 등 투자 전략 요인까지 복합적으로 작용한 탓. 한편, 최근 당국이 달러 과다 보유 기업에 대한 정책금융 지원 차별화 방안을 검토 중이란 소식 확인. 핵심은 해당 조치가 기업이 '달러를 보유함으로써 얻는 이익'보다 더 강한 유인을 제공할 수 있을지 여부</t>
+  </si>
+  <si>
+    <t>단단히 꼬인 원화의 실타래 [금일 달러/원 환율 1,460~1,470원 전망]</t>
+  </si>
+  <si>
+    <t>[달러/원 환율] 대외적 여건은 원화 강세에 우호적, 수급과 심리가 변수 전일 달러/원 환율은 연준 금리인하 기대에 따른 달러 약세 압력에 1,462원으로 하락 개장. 하지만 월말임에도 수출 네고 물량이 더디게 출회되는 가운데, 국내증시에서는 외국인 순매도세가 나타나며 환율도 상승으로 전환. 당국 경계에 1,470원이 상단으로 작용, 전일 종가 대비 5.7원 상승한 1,470.6원에 정규장 마감. 야간장에서는 미일 통화정책 차별화 기대에 따른 달러 약세에 하락하며 1,466.8원으로 마감. 역외 NDF 환율은 3.40원 하락한 1,464.75원에 최종 호가 금일 달러/원 환율은 주말간 달러 약세와 역외 거래를 감안해 1,460원대 하락 개장 예상. 연준 금리인하 기대가 지속되며 약 달러 분위기. 일본 엔화는 BOJ 인상 기대에 강세 전환 시도 중. 더불어 위험선호심리는 뉴욕증시 호조 등에 회복 국면. 약 달러·엔 반등·위험선호 조합은 원화에 긍정적. 다만 여전히 꼬여있는 수급과 잔존한 롱 심리가 하단 지지. 달러/원은 대외적 하락 압력과 대내적 하방 경직 요인 대치하며 등락 예상 [글로벌 동향] 캐나다 성장 호조, 미일 통화정책 차별화 기대에 약 달러 전일 미 달러화는 캐나다 경제성장률 호조와 미일 통화정책 차별화 기대에 약세. 주요 6개국 통화로 구성된 달러화 지수는 0.11% 하락한 99.46pt 기록. 캐나다의 3분기 실질 GDP는 전기비 연율 2.6% 증가. 이는 예상치 (+0.5%) 및 전기치 (-1.8%)를 모두 큰 폭으로 상회한 수치. 이에 캐나다 달러는 미 달러 대비 0.41% 절상, 환율은 1.4달러를 하회. 한편 시장에서는 12월 미국 및 일본의 통화정책 차별화를 기대하는 모습. OIS 시장에서 연준 금리인하 확률은 88%, BOJ 금리인상 확률은 61%로 반영. 연준 위원들의 발언이나 경제지표는 없었으나, 시장은 연준의 12월 금리인하 기대. 한편 일본 정부는 경기부양 위한 18조 3천억엔 규모 추경 승인. 이에 따른 국채발행 부담에 10년물 국채금리는 1.8%를 상회. 하지만 달러/엔 환율은 미일 금리차 축소 기대 등에 156엔대 초반까지 하락 [마켓 이슈] 상하단 모두 막힌 달러/원, 역내 수급 상황과 미 고용지표 주시 그동안 급격하게 상승했던 달러/원 환율은 최근 들어 상승세가 다소 진정. 외환당국의 강력한 시장 안정 메시지와 한국은행의 매파적 기조, 국민연금의 전략적 환 헤지 경계 등에 1,480원이 상단으로 인식되는 상황. 하지만 달러/원의 하단 역시 단단한 모습. 여전히 역내 시장에서는 달러 매수 우위 장세가 지속. 수출업체의 래깅 (lagging) 전략으로 역내 달러 공급이 부족. 반면 외국인의 국내 증시 이탈과 거주자의 해외투자 등으로 달러 수요는 증가. 11월 한 달 간 외국인 주식 순매도액은 97억 달러. 같은 기간 거주자 해외주식 순매수액은 55억 달러. 즉, 국내외 증시에서 한 달 동안 약 150억 달러 규모의 순유출 압력에 노출. 당분간 이러한 수급 불균형 상태가 이어지며 달러/원 하방은 제한적. 더불어 FOMC를 일주일 앞두고 발표될 미국 고용지표 (ADP 민간고용, ISM 고용지수) 결과도 주시 필요. 금주는 1,450~1,480원 박스권 예상</t>
+  </si>
 </sst>
 </file>
 
@@ -27637,7 +27680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A259CB23-3A24-4338-82D5-59F8A624BFCA}">
-  <dimension ref="A1:G3338"/>
+  <dimension ref="A1:G3337"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
@@ -73039,7 +73082,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3233" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3233" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3233" s="3">
         <v>45976</v>
       </c>
@@ -73053,7 +73096,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3234" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3234" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3234" s="3">
         <v>45977</v>
       </c>
@@ -73067,7 +73110,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3235" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3235" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3235" s="3">
         <v>45978</v>
       </c>
@@ -73081,7 +73124,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3236" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3236" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3236" s="3">
         <v>45979</v>
       </c>
@@ -73095,7 +73138,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3237" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3237" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3237" s="3">
         <v>45980</v>
       </c>
@@ -73109,7 +73152,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3238" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3238" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3238" s="3">
         <v>45981</v>
       </c>
@@ -73123,7 +73166,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3239" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3239" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3239" s="3">
         <v>45982</v>
       </c>
@@ -73137,7 +73180,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3240" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3240" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3240" s="3">
         <v>45983</v>
       </c>
@@ -73151,7 +73194,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3241" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3241" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3241" s="3">
         <v>45984</v>
       </c>
@@ -73165,7 +73208,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3242" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3242" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3242" s="3">
         <v>45985</v>
       </c>
@@ -73179,7 +73222,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3243" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3243" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3243" s="3">
         <v>45986</v>
       </c>
@@ -73193,7 +73236,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3244" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3244" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3244" s="3">
         <v>45987</v>
       </c>
@@ -73207,7 +73250,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3245" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3245" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3245" s="3">
         <v>45988</v>
       </c>
@@ -73221,7 +73264,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3246" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3246" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3246" s="3">
         <v>45989</v>
       </c>
@@ -73235,12 +73278,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3247" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3247" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3247" s="3">
-        <v>45990</v>
+        <v>45992</v>
       </c>
       <c r="B3247" s="3">
-        <v>45990</v>
+        <v>45992</v>
       </c>
       <c r="C3247" s="7">
         <v>0.36805555555555558</v>
@@ -73248,83 +73291,137 @@
       <c r="D3247" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3248" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E3247" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F3247" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G3247" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3248" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3248" s="3">
-        <v>45991</v>
+        <v>45993</v>
       </c>
       <c r="B3248" s="3">
-        <v>45991</v>
+        <v>45993</v>
       </c>
       <c r="C3248" s="7">
         <v>0.36805555555555558</v>
       </c>
       <c r="D3248" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="E3248" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3248" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3248" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3249" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3249" s="3">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B3249" s="3">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="C3249" s="7">
         <v>0.36805555555555558</v>
       </c>
       <c r="D3249" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="E3249" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3249" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G3249" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3250" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3250" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B3250" s="3">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="C3250" s="7">
         <v>0.36805555555555558</v>
       </c>
       <c r="D3250" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="E3250" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3250" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G3250" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3251" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3251" s="3">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B3251" s="3">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="C3251" s="7">
         <v>0.36805555555555558</v>
       </c>
       <c r="D3251" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="E3251" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3251" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3251" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3252" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3252" s="3">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B3252" s="3">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="C3252" s="7">
         <v>0.36805555555555558</v>
       </c>
       <c r="D3252" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="E3252" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3252" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3252" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3253" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3253" s="3">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B3253" s="3">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="C3253" s="7">
         <v>0.36805555555555558</v>
@@ -73333,10 +73430,10 @@
         <v>44</v>
       </c>
       <c r="E3253" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F3253" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G3253" s="1" t="s">
         <v>17</v>
@@ -73344,10 +73441,10 @@
     </row>
     <row r="3254" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3254" s="3">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B3254" s="3">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="C3254" s="7">
         <v>0.36805555555555558</v>
@@ -73356,21 +73453,21 @@
         <v>44</v>
       </c>
       <c r="E3254" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F3254" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G3254" s="1" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3255" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3255" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B3255" s="3">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C3255" s="7">
         <v>0.36805555555555558</v>
@@ -73379,21 +73476,21 @@
         <v>44</v>
       </c>
       <c r="E3255" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F3255" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G3255" s="1" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3256" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3256" s="3">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B3256" s="3">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C3256" s="7">
         <v>0.36805555555555558</v>
@@ -73402,10 +73499,10 @@
         <v>44</v>
       </c>
       <c r="E3256" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F3256" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G3256" s="1" t="s">
         <v>192</v>
@@ -73413,10 +73510,10 @@
     </row>
     <row r="3257" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3257" s="3">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B3257" s="3">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="C3257" s="7">
         <v>0.36805555555555558</v>
@@ -73425,10 +73522,10 @@
         <v>44</v>
       </c>
       <c r="E3257" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F3257" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G3257" s="1" t="s">
         <v>192</v>
@@ -73436,10 +73533,10 @@
     </row>
     <row r="3258" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3258" s="3">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B3258" s="3">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="C3258" s="7">
         <v>0.36805555555555558</v>
@@ -73448,10 +73545,10 @@
         <v>44</v>
       </c>
       <c r="E3258" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F3258" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G3258" s="1" t="s">
         <v>192</v>
@@ -73459,10 +73556,10 @@
     </row>
     <row r="3259" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3259" s="3">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B3259" s="3">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="C3259" s="7">
         <v>0.36805555555555558</v>
@@ -73471,10 +73568,10 @@
         <v>44</v>
       </c>
       <c r="E3259" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F3259" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G3259" s="1" t="s">
         <v>192</v>
@@ -73482,10 +73579,10 @@
     </row>
     <row r="3260" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3260" s="3">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B3260" s="3">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C3260" s="7">
         <v>0.36805555555555558</v>
@@ -73494,10 +73591,10 @@
         <v>44</v>
       </c>
       <c r="E3260" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F3260" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G3260" s="1" t="s">
         <v>192</v>
@@ -73505,10 +73602,10 @@
     </row>
     <row r="3261" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3261" s="3">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B3261" s="3">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C3261" s="7">
         <v>0.36805555555555558</v>
@@ -73517,21 +73614,21 @@
         <v>44</v>
       </c>
       <c r="E3261" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F3261" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G3261" s="1" t="s">
-        <v>192</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3262" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3262" s="3">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B3262" s="3">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="C3262" s="7">
         <v>0.36805555555555558</v>
@@ -73540,10 +73637,10 @@
         <v>44</v>
       </c>
       <c r="E3262" s="1" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="F3262" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="G3262" s="1" t="s">
         <v>192</v>
@@ -73551,10 +73648,10 @@
     </row>
     <row r="3263" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3263" s="3">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B3263" s="3">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C3263" s="7">
         <v>0.36805555555555558</v>
@@ -73563,21 +73660,21 @@
         <v>44</v>
       </c>
       <c r="E3263" s="1" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="F3263" s="1" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="G3263" s="1" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3264" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3264" s="3">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B3264" s="3">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="C3264" s="7">
         <v>0.36805555555555558</v>
@@ -73586,21 +73683,21 @@
         <v>44</v>
       </c>
       <c r="E3264" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F3264" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G3264" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3265" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3265" s="3">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B3265" s="3">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="C3265" s="7">
         <v>0.36805555555555558</v>
@@ -73609,10 +73706,10 @@
         <v>44</v>
       </c>
       <c r="E3265" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F3265" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G3265" s="1" t="s">
         <v>193</v>
@@ -73620,10 +73717,10 @@
     </row>
     <row r="3266" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3266" s="3">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B3266" s="3">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C3266" s="7">
         <v>0.36805555555555558</v>
@@ -73632,21 +73729,21 @@
         <v>44</v>
       </c>
       <c r="E3266" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F3266" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G3266" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3267" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3267" s="3">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B3267" s="3">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="C3267" s="7">
         <v>0.36805555555555558</v>
@@ -73655,10 +73752,10 @@
         <v>44</v>
       </c>
       <c r="E3267" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F3267" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G3267" s="1" t="s">
         <v>193</v>
@@ -73666,10 +73763,10 @@
     </row>
     <row r="3268" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3268" s="3">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B3268" s="3">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="C3268" s="7">
         <v>0.36805555555555558</v>
@@ -73678,10 +73775,10 @@
         <v>44</v>
       </c>
       <c r="E3268" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F3268" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G3268" s="1" t="s">
         <v>192</v>
@@ -73689,10 +73786,10 @@
     </row>
     <row r="3269" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3269" s="3">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B3269" s="3">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="C3269" s="7">
         <v>0.36805555555555558</v>
@@ -73701,21 +73798,21 @@
         <v>44</v>
       </c>
       <c r="E3269" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F3269" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G3269" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3270" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3270" s="3">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B3270" s="3">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="C3270" s="7">
         <v>0.36805555555555558</v>
@@ -73724,10 +73821,10 @@
         <v>44</v>
       </c>
       <c r="E3270" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F3270" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G3270" s="1" t="s">
         <v>192</v>
@@ -73735,10 +73832,10 @@
     </row>
     <row r="3271" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3271" s="3">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B3271" s="3">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="C3271" s="7">
         <v>0.36805555555555558</v>
@@ -73747,10 +73844,10 @@
         <v>44</v>
       </c>
       <c r="E3271" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F3271" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G3271" s="1" t="s">
         <v>192</v>
@@ -73758,10 +73855,10 @@
     </row>
     <row r="3272" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3272" s="3">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B3272" s="3">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="C3272" s="7">
         <v>0.36805555555555558</v>
@@ -73770,10 +73867,10 @@
         <v>44</v>
       </c>
       <c r="E3272" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F3272" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G3272" s="1" t="s">
         <v>192</v>
@@ -73781,10 +73878,10 @@
     </row>
     <row r="3273" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3273" s="3">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B3273" s="3">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="C3273" s="7">
         <v>0.36805555555555558</v>
@@ -73793,10 +73890,10 @@
         <v>44</v>
       </c>
       <c r="E3273" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F3273" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G3273" s="1" t="s">
         <v>192</v>
@@ -73804,10 +73901,10 @@
     </row>
     <row r="3274" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3274" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B3274" s="3">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="C3274" s="7">
         <v>0.36805555555555558</v>
@@ -73816,10 +73913,10 @@
         <v>44</v>
       </c>
       <c r="E3274" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F3274" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G3274" s="1" t="s">
         <v>192</v>
@@ -73827,10 +73924,10 @@
     </row>
     <row r="3275" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3275" s="3">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B3275" s="3">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="C3275" s="7">
         <v>0.36805555555555558</v>
@@ -73839,10 +73936,10 @@
         <v>44</v>
       </c>
       <c r="E3275" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F3275" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G3275" s="1" t="s">
         <v>192</v>
@@ -73850,10 +73947,10 @@
     </row>
     <row r="3276" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3276" s="3">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B3276" s="3">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="C3276" s="7">
         <v>0.36805555555555558</v>
@@ -73862,10 +73959,10 @@
         <v>44</v>
       </c>
       <c r="E3276" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F3276" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G3276" s="1" t="s">
         <v>192</v>
@@ -73873,10 +73970,10 @@
     </row>
     <row r="3277" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3277" s="3">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B3277" s="3">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="C3277" s="7">
         <v>0.36805555555555558</v>
@@ -73885,10 +73982,10 @@
         <v>44</v>
       </c>
       <c r="E3277" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F3277" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G3277" s="1" t="s">
         <v>192</v>
@@ -73896,10 +73993,10 @@
     </row>
     <row r="3278" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3278" s="3">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B3278" s="3">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="C3278" s="7">
         <v>0.36805555555555558</v>
@@ -73908,10 +74005,10 @@
         <v>44</v>
       </c>
       <c r="E3278" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F3278" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G3278" s="1" t="s">
         <v>192</v>
@@ -73919,10 +74016,10 @@
     </row>
     <row r="3279" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3279" s="3">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B3279" s="3">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="C3279" s="7">
         <v>0.36805555555555558</v>
@@ -73931,10 +74028,10 @@
         <v>44</v>
       </c>
       <c r="E3279" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F3279" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G3279" s="1" t="s">
         <v>192</v>
@@ -73942,10 +74039,10 @@
     </row>
     <row r="3280" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3280" s="3">
-        <v>46037</v>
+        <v>46041</v>
       </c>
       <c r="B3280" s="3">
-        <v>46037</v>
+        <v>46041</v>
       </c>
       <c r="C3280" s="7">
         <v>0.36805555555555558</v>
@@ -73954,10 +74051,10 @@
         <v>44</v>
       </c>
       <c r="E3280" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F3280" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G3280" s="1" t="s">
         <v>192</v>
@@ -73965,10 +74062,10 @@
     </row>
     <row r="3281" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3281" s="3">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B3281" s="3">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="C3281" s="7">
         <v>0.36805555555555558</v>
@@ -73977,10 +74074,10 @@
         <v>44</v>
       </c>
       <c r="E3281" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F3281" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G3281" s="1" t="s">
         <v>192</v>
@@ -73988,10 +74085,10 @@
     </row>
     <row r="3282" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3282" s="3">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="B3282" s="3">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="C3282" s="7">
         <v>0.36805555555555558</v>
@@ -74000,10 +74097,10 @@
         <v>44</v>
       </c>
       <c r="E3282" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F3282" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G3282" s="1" t="s">
         <v>192</v>
@@ -74011,10 +74108,10 @@
     </row>
     <row r="3283" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3283" s="3">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B3283" s="3">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="C3283" s="7">
         <v>0.36805555555555558</v>
@@ -74023,10 +74120,10 @@
         <v>44</v>
       </c>
       <c r="E3283" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F3283" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G3283" s="1" t="s">
         <v>192</v>
@@ -74034,10 +74131,10 @@
     </row>
     <row r="3284" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3284" s="3">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B3284" s="3">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="C3284" s="7">
         <v>0.36805555555555558</v>
@@ -74046,10 +74143,10 @@
         <v>44</v>
       </c>
       <c r="E3284" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F3284" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G3284" s="1" t="s">
         <v>192</v>
@@ -74057,10 +74154,10 @@
     </row>
     <row r="3285" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3285" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B3285" s="3">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="C3285" s="7">
         <v>0.36805555555555558</v>
@@ -74069,10 +74166,10 @@
         <v>44</v>
       </c>
       <c r="E3285" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F3285" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G3285" s="1" t="s">
         <v>192</v>
@@ -74080,10 +74177,10 @@
     </row>
     <row r="3286" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3286" s="3">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B3286" s="3">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="C3286" s="7">
         <v>0.36805555555555558</v>
@@ -74092,10 +74189,10 @@
         <v>44</v>
       </c>
       <c r="E3286" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F3286" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G3286" s="1" t="s">
         <v>192</v>
@@ -74103,10 +74200,10 @@
     </row>
     <row r="3287" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3287" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B3287" s="3">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="C3287" s="7">
         <v>0.36805555555555558</v>
@@ -74115,10 +74212,10 @@
         <v>44</v>
       </c>
       <c r="E3287" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F3287" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G3287" s="1" t="s">
         <v>192</v>
@@ -74126,10 +74223,10 @@
     </row>
     <row r="3288" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3288" s="3">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B3288" s="3">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="C3288" s="7">
         <v>0.36805555555555558</v>
@@ -74138,10 +74235,10 @@
         <v>44</v>
       </c>
       <c r="E3288" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F3288" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G3288" s="1" t="s">
         <v>192</v>
@@ -74149,10 +74246,10 @@
     </row>
     <row r="3289" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3289" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B3289" s="3">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="C3289" s="7">
         <v>0.36805555555555558</v>
@@ -74161,10 +74258,10 @@
         <v>44</v>
       </c>
       <c r="E3289" s="1" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F3289" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G3289" s="1" t="s">
         <v>192</v>
@@ -74172,10 +74269,10 @@
     </row>
     <row r="3290" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3290" s="3">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B3290" s="3">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="C3290" s="7">
         <v>0.36805555555555558</v>
@@ -74184,10 +74281,10 @@
         <v>44</v>
       </c>
       <c r="E3290" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F3290" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G3290" s="1" t="s">
         <v>192</v>
@@ -74195,10 +74292,10 @@
     </row>
     <row r="3291" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3291" s="3">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B3291" s="3">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="C3291" s="7">
         <v>0.36805555555555558</v>
@@ -74207,10 +74304,10 @@
         <v>44</v>
       </c>
       <c r="E3291" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F3291" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G3291" s="1" t="s">
         <v>192</v>
@@ -74218,10 +74315,10 @@
     </row>
     <row r="3292" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3292" s="3">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B3292" s="3">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="C3292" s="7">
         <v>0.36805555555555558</v>
@@ -74230,10 +74327,10 @@
         <v>44</v>
       </c>
       <c r="E3292" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F3292" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G3292" s="1" t="s">
         <v>192</v>
@@ -74241,10 +74338,10 @@
     </row>
     <row r="3293" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3293" s="3">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B3293" s="3">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="C3293" s="7">
         <v>0.36805555555555558</v>
@@ -74253,21 +74350,21 @@
         <v>44</v>
       </c>
       <c r="E3293" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F3293" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G3293" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3294" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3294" s="3">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B3294" s="3">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="C3294" s="7">
         <v>0.36805555555555558</v>
@@ -74276,21 +74373,21 @@
         <v>44</v>
       </c>
       <c r="E3294" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F3294" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G3294" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3295" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3295" s="3">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B3295" s="3">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="C3295" s="7">
         <v>0.36805555555555558</v>
@@ -74299,21 +74396,21 @@
         <v>44</v>
       </c>
       <c r="E3295" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F3295" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G3295" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3296" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3296" s="3">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B3296" s="3">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="C3296" s="7">
         <v>0.36805555555555558</v>
@@ -74322,10 +74419,10 @@
         <v>44</v>
       </c>
       <c r="E3296" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F3296" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G3296" s="1" t="s">
         <v>193</v>
@@ -74333,10 +74430,10 @@
     </row>
     <row r="3297" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3297" s="3">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B3297" s="3">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="C3297" s="7">
         <v>0.36805555555555558</v>
@@ -74345,10 +74442,10 @@
         <v>44</v>
       </c>
       <c r="E3297" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F3297" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G3297" s="1" t="s">
         <v>192</v>
@@ -74356,10 +74453,10 @@
     </row>
     <row r="3298" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3298" s="3">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B3298" s="3">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="C3298" s="7">
         <v>0.36805555555555558</v>
@@ -74368,21 +74465,21 @@
         <v>44</v>
       </c>
       <c r="E3298" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F3298" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G3298" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3299" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3299" s="3">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B3299" s="3">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="C3299" s="7">
         <v>0.36805555555555558</v>
@@ -74391,10 +74488,10 @@
         <v>44</v>
       </c>
       <c r="E3299" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F3299" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G3299" s="1" t="s">
         <v>192</v>
@@ -74402,10 +74499,10 @@
     </row>
     <row r="3300" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3300" s="3">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="B3300" s="3">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="C3300" s="7">
         <v>0.36805555555555558</v>
@@ -74414,10 +74511,10 @@
         <v>44</v>
       </c>
       <c r="E3300" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F3300" s="1" t="s">
-        <v>43</v>
+        <v>194</v>
       </c>
       <c r="G3300" s="1" t="s">
         <v>192</v>
@@ -74425,10 +74522,10 @@
     </row>
     <row r="3301" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3301" s="3">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="B3301" s="3">
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="C3301" s="7">
         <v>0.36805555555555558</v>
@@ -74437,10 +74534,10 @@
         <v>44</v>
       </c>
       <c r="E3301" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F3301" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G3301" s="1" t="s">
         <v>192</v>
@@ -74448,10 +74545,10 @@
     </row>
     <row r="3302" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3302" s="3">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B3302" s="3">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="C3302" s="7">
         <v>0.36805555555555558</v>
@@ -74460,10 +74557,10 @@
         <v>44</v>
       </c>
       <c r="E3302" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F3302" s="1" t="s">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="G3302" s="1" t="s">
         <v>192</v>
@@ -74471,10 +74568,10 @@
     </row>
     <row r="3303" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3303" s="3">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B3303" s="3">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="C3303" s="7">
         <v>0.36805555555555558</v>
@@ -74483,10 +74580,10 @@
         <v>44</v>
       </c>
       <c r="E3303" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F3303" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G3303" s="1" t="s">
         <v>192</v>
@@ -74494,10 +74591,10 @@
     </row>
     <row r="3304" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3304" s="3">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B3304" s="3">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="C3304" s="7">
         <v>0.36805555555555558</v>
@@ -74506,10 +74603,10 @@
         <v>44</v>
       </c>
       <c r="E3304" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F3304" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G3304" s="1" t="s">
         <v>192</v>
@@ -74517,10 +74614,10 @@
     </row>
     <row r="3305" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3305" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B3305" s="3">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C3305" s="7">
         <v>0.36805555555555558</v>
@@ -74529,10 +74626,10 @@
         <v>44</v>
       </c>
       <c r="E3305" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F3305" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G3305" s="1" t="s">
         <v>192</v>
@@ -74540,10 +74637,10 @@
     </row>
     <row r="3306" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3306" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B3306" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="C3306" s="7">
         <v>0.36805555555555558</v>
@@ -74552,10 +74649,10 @@
         <v>44</v>
       </c>
       <c r="E3306" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F3306" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G3306" s="1" t="s">
         <v>192</v>
@@ -74563,10 +74660,10 @@
     </row>
     <row r="3307" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3307" s="3">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="B3307" s="3">
-        <v>46079</v>
+        <v>46084</v>
       </c>
       <c r="C3307" s="7">
         <v>0.36805555555555558</v>
@@ -74575,10 +74672,10 @@
         <v>44</v>
       </c>
       <c r="E3307" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3307" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G3307" s="1" t="s">
         <v>192</v>
@@ -74586,10 +74683,10 @@
     </row>
     <row r="3308" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3308" s="3">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="B3308" s="3">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="C3308" s="7">
         <v>0.36805555555555558</v>
@@ -74598,21 +74695,21 @@
         <v>44</v>
       </c>
       <c r="E3308" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F3308" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G3308" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3309" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3309" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B3309" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="C3309" s="7">
         <v>0.36805555555555558</v>
@@ -74621,21 +74718,21 @@
         <v>44</v>
       </c>
       <c r="E3309" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F3309" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G3309" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3310" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3310" s="3">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B3310" s="3">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="C3310" s="7">
         <v>0.36805555555555558</v>
@@ -74644,21 +74741,21 @@
         <v>44</v>
       </c>
       <c r="E3310" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3310" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G3310" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3311" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3311" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B3311" s="3">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="C3311" s="7">
         <v>0.36805555555555558</v>
@@ -74667,21 +74764,21 @@
         <v>44</v>
       </c>
       <c r="E3311" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F3311" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G3311" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3312" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3312" s="3">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B3312" s="3">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="C3312" s="7">
         <v>0.36805555555555558</v>
@@ -74690,10 +74787,10 @@
         <v>44</v>
       </c>
       <c r="E3312" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F3312" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G3312" s="1" t="s">
         <v>192</v>
@@ -74701,10 +74798,10 @@
     </row>
     <row r="3313" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3313" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B3313" s="3">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="C3313" s="7">
         <v>0.36805555555555558</v>
@@ -74713,10 +74810,10 @@
         <v>44</v>
       </c>
       <c r="E3313" s="1" t="s">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="F3313" s="1" t="s">
-        <v>15</v>
+        <v>195</v>
       </c>
       <c r="G3313" s="1" t="s">
         <v>192</v>
@@ -74724,22 +74821,22 @@
     </row>
     <row r="3314" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3314" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B3314" s="3">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="C3314" s="7">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3314" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="E3314" s="1" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="F3314" s="1" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="G3314" s="1" t="s">
         <v>192</v>
@@ -74747,33 +74844,33 @@
     </row>
     <row r="3315" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3315" s="3">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B3315" s="3">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="C3315" s="7">
-        <v>0.36805555555555558</v>
+        <v>0.36805555555555602</v>
       </c>
       <c r="D3315" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="E3315" s="1" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="F3315" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G3315" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3316" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3316" s="3">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B3316" s="3">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="C3316" s="7">
         <v>0.36805555555555602</v>
@@ -74782,10 +74879,10 @@
         <v>67</v>
       </c>
       <c r="E3316" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F3316" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G3316" s="1" t="s">
         <v>192</v>
@@ -74793,10 +74890,10 @@
     </row>
     <row r="3317" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3317" s="3">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B3317" s="3">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="C3317" s="7">
         <v>0.36805555555555602</v>
@@ -74805,10 +74902,10 @@
         <v>67</v>
       </c>
       <c r="E3317" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F3317" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G3317" s="1" t="s">
         <v>193</v>
@@ -74816,10 +74913,10 @@
     </row>
     <row r="3318" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3318" s="3">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B3318" s="3">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="C3318" s="7">
         <v>0.36805555555555602</v>
@@ -74828,10 +74925,10 @@
         <v>67</v>
       </c>
       <c r="E3318" s="1" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="F3318" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G3318" s="1" t="s">
         <v>192</v>
@@ -74839,10 +74936,10 @@
     </row>
     <row r="3319" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3319" s="3">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B3319" s="3">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="C3319" s="7">
         <v>0.36805555555555602</v>
@@ -74851,21 +74948,21 @@
         <v>67</v>
       </c>
       <c r="E3319" s="1" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="F3319" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G3319" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3320" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3320" s="3">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B3320" s="3">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="C3320" s="7">
         <v>0.36805555555555602</v>
@@ -74874,10 +74971,10 @@
         <v>67</v>
       </c>
       <c r="E3320" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F3320" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G3320" s="1" t="s">
         <v>192</v>
@@ -74885,10 +74982,10 @@
     </row>
     <row r="3321" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3321" s="3">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B3321" s="3">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="C3321" s="7">
         <v>0.36805555555555602</v>
@@ -74897,10 +74994,10 @@
         <v>67</v>
       </c>
       <c r="E3321" s="1" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="F3321" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G3321" s="1" t="s">
         <v>192</v>
@@ -74908,10 +75005,10 @@
     </row>
     <row r="3322" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3322" s="3">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B3322" s="3">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="C3322" s="7">
         <v>0.36805555555555602</v>
@@ -74920,10 +75017,10 @@
         <v>67</v>
       </c>
       <c r="E3322" s="1" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F3322" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G3322" s="1" t="s">
         <v>192</v>
@@ -74931,10 +75028,10 @@
     </row>
     <row r="3323" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3323" s="3">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B3323" s="3">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="C3323" s="7">
         <v>0.36805555555555602</v>
@@ -74943,10 +75040,10 @@
         <v>67</v>
       </c>
       <c r="E3323" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F3323" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G3323" s="1" t="s">
         <v>192</v>
@@ -74954,10 +75051,10 @@
     </row>
     <row r="3324" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3324" s="3">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B3324" s="3">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C3324" s="7">
         <v>0.36805555555555602</v>
@@ -74966,10 +75063,10 @@
         <v>67</v>
       </c>
       <c r="E3324" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F3324" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G3324" s="1" t="s">
         <v>192</v>
@@ -74977,10 +75074,10 @@
     </row>
     <row r="3325" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3325" s="3">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B3325" s="3">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="C3325" s="7">
         <v>0.36805555555555602</v>
@@ -74989,10 +75086,10 @@
         <v>67</v>
       </c>
       <c r="E3325" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F3325" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G3325" s="1" t="s">
         <v>192</v>
@@ -75000,10 +75097,10 @@
     </row>
     <row r="3326" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3326" s="3">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B3326" s="3">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="C3326" s="7">
         <v>0.36805555555555602</v>
@@ -75012,10 +75109,10 @@
         <v>67</v>
       </c>
       <c r="E3326" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F3326" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G3326" s="1" t="s">
         <v>192</v>
@@ -75023,10 +75120,10 @@
     </row>
     <row r="3327" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3327" s="3">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B3327" s="3">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="C3327" s="7">
         <v>0.36805555555555602</v>
@@ -75035,10 +75132,10 @@
         <v>67</v>
       </c>
       <c r="E3327" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F3327" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G3327" s="1" t="s">
         <v>192</v>
@@ -75046,10 +75143,10 @@
     </row>
     <row r="3328" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3328" s="3">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B3328" s="3">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="C3328" s="7">
         <v>0.36805555555555602</v>
@@ -75058,10 +75155,10 @@
         <v>67</v>
       </c>
       <c r="E3328" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F3328" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G3328" s="1" t="s">
         <v>192</v>
@@ -75069,10 +75166,10 @@
     </row>
     <row r="3329" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3329" s="3">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B3329" s="3">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="C3329" s="7">
         <v>0.36805555555555602</v>
@@ -75081,10 +75178,10 @@
         <v>67</v>
       </c>
       <c r="E3329" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F3329" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G3329" s="1" t="s">
         <v>192</v>
@@ -75092,10 +75189,10 @@
     </row>
     <row r="3330" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3330" s="3">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="B3330" s="3">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="C3330" s="7">
         <v>0.36805555555555602</v>
@@ -75104,10 +75201,10 @@
         <v>67</v>
       </c>
       <c r="E3330" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F3330" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G3330" s="1" t="s">
         <v>192</v>
@@ -75115,10 +75212,10 @@
     </row>
     <row r="3331" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3331" s="3">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B3331" s="3">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="C3331" s="7">
         <v>0.36805555555555602</v>
@@ -75127,10 +75224,10 @@
         <v>67</v>
       </c>
       <c r="E3331" s="1" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F3331" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G3331" s="1" t="s">
         <v>192</v>
@@ -75138,10 +75235,10 @@
     </row>
     <row r="3332" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3332" s="3">
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="B3332" s="3">
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="C3332" s="7">
         <v>0.36805555555555602</v>
@@ -75150,10 +75247,10 @@
         <v>67</v>
       </c>
       <c r="E3332" s="1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F3332" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G3332" s="1" t="s">
         <v>192</v>
@@ -75161,10 +75258,10 @@
     </row>
     <row r="3333" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3333" s="3">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B3333" s="3">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="C3333" s="7">
         <v>0.36805555555555602</v>
@@ -75173,10 +75270,10 @@
         <v>67</v>
       </c>
       <c r="E3333" s="1" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="F3333" s="1" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="G3333" s="1" t="s">
         <v>192</v>
@@ -75184,10 +75281,10 @@
     </row>
     <row r="3334" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3334" s="3">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B3334" s="3">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="C3334" s="7">
         <v>0.36805555555555602</v>
@@ -75196,10 +75293,10 @@
         <v>67</v>
       </c>
       <c r="E3334" s="1" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="F3334" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G3334" s="1" t="s">
         <v>192</v>
@@ -75207,10 +75304,10 @@
     </row>
     <row r="3335" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3335" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B3335" s="3">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C3335" s="7">
         <v>0.36805555555555602</v>
@@ -75219,21 +75316,21 @@
         <v>67</v>
       </c>
       <c r="E3335" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F3335" s="1" t="s">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="G3335" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3336" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3336" s="3">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B3336" s="3">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="C3336" s="7">
         <v>0.36805555555555602</v>
@@ -75242,10 +75339,10 @@
         <v>67</v>
       </c>
       <c r="E3336" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F3336" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G3336" s="1" t="s">
         <v>192</v>
@@ -75253,10 +75350,10 @@
     </row>
     <row r="3337" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3337" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B3337" s="3">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="C3337" s="7">
         <v>0.36805555555555602</v>
@@ -75265,36 +75362,13 @@
         <v>67</v>
       </c>
       <c r="E3337" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F3337" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="G3337" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3338" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3338" s="3">
-        <v>46125</v>
-      </c>
-      <c r="B3338" s="3">
-        <v>46125</v>
-      </c>
-      <c r="C3338" s="7">
-        <v>0.36805555555555602</v>
-      </c>
-      <c r="D3338" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3338" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F3338" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="G3338" s="1" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
